--- a/results/link-prediction-gcn/Link/0shot/Wisconsin/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/0shot/Wisconsin/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>0.5625±0.0884</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.5208±0.0295</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0354</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0547</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0354</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0687</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0520</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.5417±0.0450</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5417±0.0450</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5417±0.0450</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0450</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.6319±0.0644</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0428</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.5903±0.1277</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.5069±0.0098</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.5069±0.0260</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0428</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0354</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0196</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.5347±0.0196</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0354</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0354</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0354</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0520</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.6042±0.0340</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.5417±0.0170</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0982</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.5278±0.0520</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0428</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.5417±0.0340</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.5278±0.0260</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5347±0.0491</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5347±0.0354</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.5347±0.0354</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.5347±0.0354</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0196</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0354</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.5417±0.0450</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.7153±0.1025</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6319±0.0687</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.6181±0.0708</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.6111±0.0354</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.6389±0.0967</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0196</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0428</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.6667±0.0340</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.6667±0.0340</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.6667±0.0340</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6458±0.0170</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.6667±0.0340</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.6736±0.0428</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.6528±0.0937</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.5208±0.0295</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.5278±0.0260</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.5278±0.0260</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0354</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.5417±0.0589</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.5208±0.0295</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.5278±0.0393</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.5278±0.0393</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.5278±0.0393</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0450</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.5972±0.0098</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.5833±0.1179</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>0.5000±0.0000</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0196</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0260</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>0.4861±0.0354</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0687</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0.5833±0.0780</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0.5208±0.0295</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0354</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0.5347±0.0260</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0982</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0884</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0687</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>0.5903±0.0687</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0450</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0295</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0597</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>0.4861±0.0260</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
         <is>
           <t>0.5208±0.0000</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>0.5208±0.0450</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0098</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0098</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0098</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0597</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>0.6250±0.1115</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
         <is>
           <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5833±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.7500±0.0000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.4792±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.5833±0.0000</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.4792±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.4792±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.4792±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.4792±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.4583±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.5833±0.0000</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.7500±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.7500±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.7500±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.7708±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.4375±0.0000</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.6875±0.0000</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.4167±0.0000</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>0.6458±0.0000</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>0.6349±0.0449</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.6550±0.0165</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.6840±0.0246</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6881±0.0238</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.6250±0.0316</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.6850±0.0300</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.6755±0.0221</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6771±0.0090</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6771±0.0090</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6771±0.0090</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6662±0.0412</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.7125±0.0260</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.6796±0.0264</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.6838±0.0242</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.6567±0.0084</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6283±0.0132</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6739±0.0051</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.6768±0.0078</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6963±0.0161</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.6372±0.0349</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6998±0.0209</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6998±0.0209</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6998±0.0209</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.6770±0.0079</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.6632±0.0201</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.6796±0.0092</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.4541±0.3213</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6572±0.0207</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6767±0.0292</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.6830±0.0167</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.6555±0.0234</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6772±0.0150</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6703±0.0051</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.6703±0.0051</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.6703±0.0051</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6468±0.0281</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.6868±0.0214</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.6804±0.0133</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.6981±0.0889</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6713±0.0590</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.7014±0.0396</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6794±0.0332</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.7236±0.0591</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6796±0.0264</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.6940±0.0129</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7275±0.0221</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7275±0.0221</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7275±0.0221</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7120±0.0099</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7211±0.0206</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7249±0.0294</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.6689±0.0391</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6733±0.0094</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6629±0.0246</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6729±0.0200</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6498±0.0168</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.6746±0.0184</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6505±0.0229</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6797±0.0185</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6797±0.0185</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6797±0.0185</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6517±0.0377</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6902±0.0248</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.7088±0.0596</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.2222±0.3143</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.6102±0.0000</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.6761±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.6857±0.0000</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6933±0.0168</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6601±0.0163</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0.6114±0.0446</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.6874±0.0363</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.6759±0.0305</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6732±0.0164</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6894±0.0166</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6692±0.0207</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.7025±0.0507</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6869±0.0286</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6649±0.0347</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>0.6803±0.0193</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.6765±0.0225</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.6592±0.0054</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.6413±0.0421</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>0.6477±0.0156</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6774±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.7143±0.0000</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.5385±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.6479±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.6552±0.0000</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0.6765±0.0000</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.7000±0.0000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.7000±0.0000</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.7000±0.0000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.7273±0.0000</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.6786±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.6923±0.0000</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6316±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6377±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.6479±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.6479±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.6479±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.6286±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.6885±0.0000</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6557±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6567±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6780±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.7164±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6970±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7097±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7857±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7857±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7857±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7000±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.8000±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.6562±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6230±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6857±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.7077±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.5846±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6857±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.7077±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6957±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6957±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6957±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6957±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6571±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.7273±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.6071±0.0000</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.5333±0.0000</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.6761±0.0000</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6481±0.0151</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6633±0.0047</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6633±0.0047</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6633±0.0047</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6777±0.0212</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7302±0.0000</t>
+          <t>0.6795±0.0731</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6796±0.0044</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.7760±0.0000</t>
+          <t>0.7558±0.0578</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7812±0.0000</t>
+          <t>0.7436±0.0844</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5642±0.0000</t>
+          <t>0.7894±0.0616</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6788±0.0000</t>
+          <t>0.7720±0.0956</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.7656±0.0000</t>
+          <t>0.7031±0.1017</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.7135±0.0000</t>
+          <t>0.7497±0.0096</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6944±0.0000</t>
+          <t>0.7685±0.1053</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.7760±0.0000</t>
+          <t>0.7448±0.0418</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7760±0.0000</t>
+          <t>0.7448±0.0418</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.7760±0.0000</t>
+          <t>0.7448±0.0418</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.7656±0.0000</t>
+          <t>0.7720±0.0721</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.5694±0.0000</t>
+          <t>0.6742±0.0843</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.7529±0.1114</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.7830±0.0000</t>
+          <t>0.7697±0.0666</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.9062±0.0000</t>
+          <t>0.7679±0.0653</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4740±0.0000</t>
+          <t>0.6282±0.0351</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6615±0.0000</t>
+          <t>0.7564±0.1061</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.7543±0.0000</t>
+          <t>0.7622±0.0272</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.7005±0.0000</t>
+          <t>0.7607±0.0613</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7812±0.0000</t>
+          <t>0.7095±0.1328</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7300±0.0000</t>
+          <t>0.8021±0.0049</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7300±0.0000</t>
+          <t>0.8021±0.0049</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7300±0.0000</t>
+          <t>0.8021±0.0049</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.8299±0.0000</t>
+          <t>0.7361±0.0931</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7135±0.0000</t>
+          <t>0.7130±0.0343</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.6476±0.0000</t>
+          <t>0.7257±0.0413</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.7587±0.0000</t>
+          <t>0.7772±0.0555</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.7934±0.0000</t>
+          <t>0.8009±0.0213</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.5608±0.0000</t>
+          <t>0.7263±0.1029</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.5868±0.0000</t>
+          <t>0.7951±0.0794</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.7370±0.0000</t>
+          <t>0.7989±0.0354</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.7619±0.0523</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.8177±0.0000</t>
+          <t>0.8027±0.0244</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.7274±0.0000</t>
+          <t>0.7859±0.0489</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.7274±0.0000</t>
+          <t>0.7859±0.0489</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.7274±0.0000</t>
+          <t>0.7859±0.0489</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.8698±0.0000</t>
+          <t>0.7436±0.0841</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.7604±0.0000</t>
+          <t>0.7465±0.0395</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.7587±0.0000</t>
+          <t>0.7471±0.0777</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6771±0.0000</t>
+          <t>0.7413±0.0583</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7205±0.0000</t>
+          <t>0.6806±0.0596</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.5026±0.0000</t>
+          <t>0.6513±0.0814</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.6007±0.0000</t>
+          <t>0.6736±0.0806</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.8061±0.1081</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.6658±0.0000</t>
+          <t>0.7491±0.0871</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.7946±0.0291</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.7700±0.0000</t>
+          <t>0.6881±0.0338</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.7700±0.0000</t>
+          <t>0.6881±0.0338</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.7700±0.0000</t>
+          <t>0.6881±0.0338</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.6910±0.0000</t>
+          <t>0.7338±0.0268</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.7309±0.0000</t>
+          <t>0.6956±0.0581</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.7639±0.0000</t>
+          <t>0.7306±0.0525</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.7153±0.0000</t>
+          <t>0.7714±0.0659</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.8090±0.0000</t>
+          <t>0.7691±0.0367</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.6102±0.0000</t>
+          <t>0.7118±0.0577</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.6858±0.0000</t>
+          <t>0.7752±0.0927</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.7396±0.0000</t>
+          <t>0.7859±0.0703</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.8142±0.0000</t>
+          <t>0.7118±0.0930</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.8299±0.0000</t>
+          <t>0.7170±0.0681</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.7726±0.0000</t>
+          <t>0.7714±0.0433</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.7726±0.0000</t>
+          <t>0.7714±0.0433</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.7726±0.0000</t>
+          <t>0.7714±0.0433</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.7899±0.0000</t>
+          <t>0.7321±0.1019</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.7431±0.0000</t>
+          <t>0.6539±0.0685</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.7986±0.0000</t>
+          <t>0.7911±0.0770</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.7361±0.0000</t>
+          <t>0.7500±0.0561</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.7587±0.0000</t>
+          <t>0.7755±0.0124</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.5469±0.0000</t>
+          <t>0.7876±0.1075</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.7361±0.0000</t>
+          <t>0.7778±0.0645</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.8333±0.0000</t>
+          <t>0.7170±0.1232</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.7656±0.0000</t>
+          <t>0.8148±0.0444</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.8403±0.0000</t>
+          <t>0.7581±0.0817</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.8785±0.0000</t>
+          <t>0.8316±0.0651</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.8785±0.0000</t>
+          <t>0.8461±0.0313</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.8785±0.0000</t>
+          <t>0.7946±0.0974</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.8351±0.0000</t>
+          <t>0.8084±0.0561</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.7743±0.0000</t>
+          <t>0.7517±0.0192</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.7344±0.0000</t>
+          <t>0.7807±0.0252</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.7326±0.0000</t>
+          <t>0.7367±0.0860</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.8698±0.0000</t>
+          <t>0.7928±0.0621</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.5382±0.0000</t>
+          <t>0.6192±0.0351</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4462±0.0000</t>
+          <t>0.6374±0.0166</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.6285±0.0000</t>
+          <t>0.7373±0.0145</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.7135±0.0000</t>
+          <t>0.7141±0.0735</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.8264±0.0000</t>
+          <t>0.6994±0.0689</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.6267±0.0000</t>
+          <t>0.6730±0.0682</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.6267±0.0000</t>
+          <t>0.6730±0.0682</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.6267±0.0000</t>
+          <t>0.6730±0.0682</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7743±0.0000</t>
+          <t>0.7888±0.0616</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.8264±0.0000</t>
+          <t>0.7228±0.0567</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.6337±0.0000</t>
+          <t>0.7344±0.0468</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.8056±0.0000</t>
+          <t>0.8098±0.0298</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.8178±0.0000</t>
+          <t>0.7981±0.0492</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5632±0.0000</t>
+          <t>0.8263±0.0474</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6014±0.0000</t>
+          <t>0.7683±0.1390</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.7927±0.0000</t>
+          <t>0.7454±0.0848</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.6730±0.0000</t>
+          <t>0.7959±0.0219</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7123±0.0000</t>
+          <t>0.8014±0.0591</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7887±0.0000</t>
+          <t>0.7540±0.0474</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7887±0.0000</t>
+          <t>0.7540±0.0474</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7887±0.0000</t>
+          <t>0.7540±0.0474</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8081±0.0000</t>
+          <t>0.7783±0.0482</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.5946±0.0000</t>
+          <t>0.6842±0.0622</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7607±0.0000</t>
+          <t>0.7629±0.1485</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.8282±0.0000</t>
+          <t>0.8185±0.0584</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.9240±0.0000</t>
+          <t>0.8066±0.0737</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5018±0.0000</t>
+          <t>0.6374±0.0354</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.6740±0.0000</t>
+          <t>0.7521±0.1303</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.7590±0.0000</t>
+          <t>0.7998±0.0270</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6752±0.0000</t>
+          <t>0.7414±0.0949</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7953±0.0000</t>
+          <t>0.7620±0.0792</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.7731±0.0330</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.7731±0.0330</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.7731±0.0330</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.8226±0.0000</t>
+          <t>0.7755±0.0657</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7516±0.0000</t>
+          <t>0.7398±0.0367</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.6205±0.0000</t>
+          <t>0.7254±0.0629</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.8010±0.0000</t>
+          <t>0.8302±0.0452</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.8348±0.0000</t>
+          <t>0.8320±0.0241</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5559±0.0000</t>
+          <t>0.7242±0.1167</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.5587±0.0000</t>
+          <t>0.8117±0.0978</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7165±0.0000</t>
+          <t>0.7923±0.0472</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.6549±0.0000</t>
+          <t>0.8145±0.0574</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.8411±0.0000</t>
+          <t>0.8218±0.0233</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.7726±0.0000</t>
+          <t>0.7883±0.0779</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.7726±0.0000</t>
+          <t>0.7883±0.0779</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.7726±0.0000</t>
+          <t>0.7883±0.0779</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.8820±0.0000</t>
+          <t>0.7784±0.0472</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.7986±0.0000</t>
+          <t>0.7745±0.0256</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.7959±0.0000</t>
+          <t>0.7731±0.0757</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.7004±0.0000</t>
+          <t>0.8186±0.0456</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.8025±0.0000</t>
+          <t>0.7060±0.0790</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5005±0.0000</t>
+          <t>0.6084±0.0633</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5595±0.0000</t>
+          <t>0.6584±0.0848</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.5854±0.0000</t>
+          <t>0.8393±0.0931</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.6028±0.0000</t>
+          <t>0.7819±0.0975</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.7373±0.0000</t>
+          <t>0.8187±0.0393</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.6919±0.0000</t>
+          <t>0.6263±0.0294</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.6919±0.0000</t>
+          <t>0.6263±0.0294</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.6919±0.0000</t>
+          <t>0.6263±0.0294</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.7180±0.0000</t>
+          <t>0.7235±0.0775</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.7331±0.0000</t>
+          <t>0.7190±0.0546</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.7059±0.0636</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.7853±0.0000</t>
+          <t>0.8317±0.0416</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.8519±0.0000</t>
+          <t>0.7752±0.0877</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5909±0.0000</t>
+          <t>0.7379±0.0782</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.6624±0.0000</t>
+          <t>0.7654±0.1083</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.6969±0.0000</t>
+          <t>0.8339±0.0272</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.8247±0.0000</t>
+          <t>0.7528±0.0631</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.8503±0.0000</t>
+          <t>0.7810±0.0362</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.7965±0.0000</t>
+          <t>0.7656±0.0721</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.7965±0.0000</t>
+          <t>0.7656±0.0721</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.7965±0.0000</t>
+          <t>0.7656±0.0721</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.8139±0.0000</t>
+          <t>0.7872±0.0629</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8045±0.0000</t>
+          <t>0.7288±0.0549</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.7979±0.0000</t>
+          <t>0.8051±0.0673</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.7940±0.0000</t>
+          <t>0.8139±0.0415</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.8104±0.0000</t>
+          <t>0.8128±0.0042</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5574±0.0000</t>
+          <t>0.7873±0.1385</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.7444±0.0000</t>
+          <t>0.7879±0.0802</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.8548±0.0000</t>
+          <t>0.7508±0.1118</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.8205±0.0000</t>
+          <t>0.8434±0.0308</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.8529±0.0000</t>
+          <t>0.8176±0.0434</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.8533±0.0000</t>
+          <t>0.8487±0.0320</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.8533±0.0000</t>
+          <t>0.8551±0.0093</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.8533±0.0000</t>
+          <t>0.8017±0.0759</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.8528±0.0000</t>
+          <t>0.8222±0.0483</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7698±0.0000</t>
+          <t>0.7630±0.0136</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7499±0.0000</t>
+          <t>0.8464±0.0149</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.7936±0.0000</t>
+          <t>0.7560±0.0950</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.8811±0.0000</t>
+          <t>0.8244±0.0300</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5341±0.0000</t>
+          <t>0.6196±0.0626</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.4872±0.0000</t>
+          <t>0.6677±0.0647</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6933±0.0000</t>
+          <t>0.7870±0.0336</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.7639±0.0000</t>
+          <t>0.7148±0.0978</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.8503±0.0000</t>
+          <t>0.7545±0.0490</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.5763±0.0000</t>
+          <t>0.7010±0.0758</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.5763±0.0000</t>
+          <t>0.7010±0.0758</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.5763±0.0000</t>
+          <t>0.7010±0.0758</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7967±0.0000</t>
+          <t>0.8178±0.0285</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.8368±0.0000</t>
+          <t>0.7796±0.0287</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.6752±0.0000</t>
+          <t>0.7491±0.0553</t>
         </is>
       </c>
     </row>
